--- a/docs/workbook-split/dateien/Import.xlsx
+++ b/docs/workbook-split/dateien/Import.xlsx
@@ -734,9 +734,8 @@
           <t>Monate aus Import</t>
         </is>
       </c>
-      <c r="D23" s="1">
-        <f>COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6)</f>
-        <v/>
+      <c r="D23" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -747,9 +746,8 @@
           <t>Stundenmonate aus Import</t>
         </is>
       </c>
-      <c r="D24" s="1">
-        <f>COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6)</f>
-        <v/>
+      <c r="D24" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -967,6 +965,8 @@
       <c r="C60" s="1" t="n"/>
       <c r="D60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
@@ -1040,9 +1040,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="C27:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
